--- a/raw_data_template.xlsx
+++ b/raw_data_template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,6 @@
     <col width="26" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
     <col width="26" customWidth="1" min="28" max="28"/>
-    <col width="26" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -549,80 +548,75 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Stock / Quantity</t>
+          <t>Parent Images</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Parent Images</t>
+          <t>Variant Images (optional)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Variant Images (optional)</t>
+          <t>Weight (kg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Weight (kg)</t>
+          <t>Length (cm)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Length (cm)</t>
+          <t>Width (cm)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Width (cm)</t>
+          <t>Height (cm)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Height (cm)</t>
+          <t>Shopee Shipping Service</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Shopee Shipping Service</t>
+          <t>Shopee Item Specifications</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Shopee Item Specifications</t>
+          <t>Lazada Item Specifications</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Lazada Item Specifications</t>
+          <t>TikTok Item Specifications</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>TikTok Item Specifications</t>
+          <t>Zalora Gender</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Zalora Gender</t>
+          <t>Zalora Sub Cat Type</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Zalora Sub Cat Type</t>
+          <t>Zalora Color Family</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Zalora Color Family</t>
+          <t>Zalora Color</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Zalora Color</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Zalora Images</t>
         </is>
@@ -690,50 +684,49 @@
           <t>Selling price, numbers only.</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Image URLs shared by all variants, separated by ' ; ' (space-semicolon-space).</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Image URLs shared by all variants, separated by ' ; ' (space-semicolon-space).</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
           <t>Image URLs specific to this one variant only, separated by ' ; '. Leave blank if none. Used for Shopee/Lazada/TikTok — Zalora uses its own separate image field below.</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Pasted as-is into Shopee's Shipping Service Details column.</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Pasted as-is into Shopee's Shipping Service Details column.</t>
+          <t>'Key=Value' pairs separated by ' ; '. Feeds Shopee's Product Specification columns only.</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; '. Feeds Shopee's Product Specification columns only.</t>
+          <t>'Key=Value' pairs separated by ' ; '. Feeds Lazada's Product Specification columns, and its Short Description bullets if that field is left blank.</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; '. Feeds Lazada's Product Specification columns, and its Short Description bullets if that field is left blank.</t>
+          <t>'Key=Value' pairs separated by ' ; '. Written to generic Specification columns in the output — TikTok's real template needs these under specific attribute-ID columns per category, so copy them over manually before uploading.</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; '. Written to generic Specification columns in the output — TikTok's real template needs these under specific attribute-ID columns per category, so copy them over manually before uploading.</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
           <t>Also used as the 'Gender' to match against your Category Mapping file, across all 4 marketplaces — not just Zalora.</t>
         </is>
       </c>
+      <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Zalora's own image set, separated by ' ; '. Zalora requires different image dimensions/crops than the other 3 marketplaces, so give it its own set here rather than reusing Parent/Variant Images.</t>
         </is>
@@ -794,30 +787,32 @@
       <c r="M3" s="3" t="n">
         <v>849000</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>https://example.com/img1.jpg ; https://example.com/img2.jpg</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>0.5</v>
+        <v>23</v>
       </c>
       <c r="R3" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>23</v>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Reguler (Cashless):18000.00, Instant:18000.00</t>
+        </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Reguler (Cashless):18000.00, Instant:18000.00</t>
+          <t>Brand=Hydro Flask ; Material=Stainless Steel</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
@@ -827,35 +822,30 @@
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>Brand=Hydro Flask ; Material=Stainless Steel</t>
+          <t>Material=Stainless Steel</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>Material=Stainless Steel</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Sports Metal Water Bottles</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>Sports Metal Water Bottles</t>
+          <t>grey</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>grey</t>
+          <t>Harbor</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>Harbor</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>https://example.com/zalora1.jpg ; https://example.com/zalora2.jpg</t>
         </is>
